--- a/data/trans_orig/CoTrAQ-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>60050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>245868</t>
+          <t>244954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>270054</t>
+          <t>269328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146697</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167738</t>
+          <t>168236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>400456</t>
+          <t>398619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>430572</t>
+          <t>430218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35236</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62608</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>52949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84154</t>
+          <t>84045</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174938</t>
+          <t>175200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203038</t>
+          <t>204507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85501</t>
+          <t>85078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268468</t>
+          <t>265728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307037</t>
+          <t>306908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>47536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198264</t>
+          <t>199999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226915</t>
+          <t>227342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80896</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96253</t>
+          <t>95595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286707</t>
+          <t>287420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318382</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62882</t>
+          <t>61393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96968</t>
+          <t>94884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71896</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114671</t>
+          <t>114790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159287</t>
+          <t>159649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107824</t>
+          <t>109403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81076</t>
+          <t>78425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>133022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180146</t>
+          <t>178271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>222294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>264002</t>
+          <t>263544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146443</t>
+          <t>148486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180613</t>
+          <t>180694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381722</t>
+          <t>381762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>433841</t>
+          <t>434523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37015</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66856</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84443</t>
+          <t>84371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118053</t>
+          <t>118415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>74882</t>
+          <t>75546</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60082</t>
+          <t>59275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84886</t>
+          <t>84670</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68444</t>
+          <t>69738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96015</t>
+          <t>97048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138597</t>
+          <t>136053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174138</t>
+          <t>175280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3001,107 +3001,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184033</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159502</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154458</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338491</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375033</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -3114,107 +3114,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215180</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158026</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134966</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>351</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>373205</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>411728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -3227,107 +3227,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>923</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>979679</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1016177</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>548</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>592100</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571780</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1521554</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1616962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -3340,580 +3340,123 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1378892</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1378892</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1378892</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>835</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>904583</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>904583</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>904583</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2283476</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2283476</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2283476</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial más desfavorable para la salud</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>184033</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>157107</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>210326</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>154458</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>130100</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>178100</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>338491</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>303929</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>377817</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial intermedia</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>215180</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>243656</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>158026</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>135744</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>182130</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>373205</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>338714</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>410745</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial más favorable para la salud</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>979679</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>944619</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1016884</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>592100</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>562098</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>620915</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1471</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1571780</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1525136</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1613385</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>1378892</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1378892</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1378892</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>904583</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>904583</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>904583</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>2283476</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2283476</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>2283476</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
@@ -3931,7 +3474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3962,7 +3505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4157,12 +3700,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4172,7 +3715,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4192,12 +3735,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4207,12 +3750,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4227,12 +3770,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40159</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68429</t>
+          <t>67385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4242,12 +3785,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +3813,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>58139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4285,12 +3828,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4305,12 +3848,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32112</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4320,12 +3863,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4340,12 +3883,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68827</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105668</t>
+          <t>103645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4355,12 +3898,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +3926,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>191763</t>
+          <t>190438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223310</t>
+          <t>221409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4398,12 +3941,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4418,12 +3961,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130823</t>
+          <t>131058</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158539</t>
+          <t>158443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4433,12 +3976,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4453,12 +3996,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>330930</t>
+          <t>333105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373968</t>
+          <t>373096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4468,12 +4011,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4156,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63126</t>
+          <t>63642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4628,12 +4171,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4648,12 +4191,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50510</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76191</t>
+          <t>76483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4663,12 +4206,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4683,12 +4226,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93548</t>
+          <t>93823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131334</t>
+          <t>130130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4698,12 +4241,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4269,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>63476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4741,12 +4284,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4761,12 +4304,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50541</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4776,12 +4319,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4796,12 +4339,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73500</t>
+          <t>75466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>108875</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4811,12 +4354,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4382,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>128453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159085</t>
+          <t>159932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4854,12 +4397,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4874,12 +4417,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72836</t>
+          <t>73376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101262</t>
+          <t>101920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4889,12 +4432,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4909,12 +4452,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209007</t>
+          <t>210267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252068</t>
+          <t>253297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4924,12 +4467,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +4612,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51314</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5084,12 +4627,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5109,7 +4652,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5124,7 +4667,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5139,12 +4682,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55480</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5154,12 +4697,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +4725,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45999</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5197,12 +4740,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5217,12 +4760,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5232,12 +4775,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5252,12 +4795,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>54970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5267,12 +4810,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +4838,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130302</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159395</t>
+          <t>158535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5310,12 +4853,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5330,12 +4873,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>51685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61928</t>
+          <t>62432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5345,12 +4888,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5365,12 +4908,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184611</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216502</t>
+          <t>217551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5380,12 +4923,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5068,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122318</t>
+          <t>122429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>163023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5540,12 +5083,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5560,12 +5103,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>98657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135389</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5575,12 +5118,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5595,12 +5138,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230364</t>
+          <t>230886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284322</t>
+          <t>282588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5610,12 +5153,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5181,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114673</t>
+          <t>113760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154006</t>
+          <t>154442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5653,12 +5196,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5673,12 +5216,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>69656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101011</t>
+          <t>101563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5688,12 +5231,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5708,12 +5251,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194068</t>
+          <t>193275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245718</t>
+          <t>244303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5723,12 +5266,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -5751,12 +5294,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191953</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>232547</t>
+          <t>235631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5766,12 +5309,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5786,12 +5329,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186825</t>
+          <t>186458</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5801,12 +5344,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5821,12 +5364,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>352664</t>
+          <t>356214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>412057</t>
+          <t>412713</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5836,12 +5379,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5524,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103981</t>
+          <t>102766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5996,12 +5539,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6016,12 +5559,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77066</t>
+          <t>75980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106242</t>
+          <t>105236</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6031,12 +5574,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6051,12 +5594,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158707</t>
+          <t>159626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196600</t>
+          <t>199387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6066,12 +5609,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -6094,12 +5637,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30279</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6109,12 +5652,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6129,12 +5672,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61883</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6144,12 +5687,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6164,12 +5707,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>73991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107503</t>
+          <t>106797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6179,12 +5722,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6207,12 +5750,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78242</t>
+          <t>78823</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6222,12 +5765,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6242,12 +5785,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44668</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>73127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6257,12 +5800,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6277,12 +5820,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>104706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142655</t>
+          <t>141533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6292,12 +5835,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -6417,7 +5960,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6427,107 +5970,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377903</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>293</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297689</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266129</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>606</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641283</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>594896</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>685604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -6540,107 +6083,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304222</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335916</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222067</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>526290</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>485297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>575416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -6653,107 +6196,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>724</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>774505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>737475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>811516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516463</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481385</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1290968</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1239293</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1338224</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -6766,580 +6309,123 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial más desfavorable para la salud</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>343595</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>310145</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>377952</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>297689</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>267246</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>326742</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>28,73%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>25,79%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>641283</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>598945</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>690350</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial intermedia</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>273836</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>338540</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>222067</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>198309</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>249711</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>526290</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>487898</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>569893</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Exposición psicosocial más favorable para la salud</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>774505</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>736066</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>812043</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>516463</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>487468</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>550896</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>49,84%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>53,16%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1290968</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1238497</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1342736</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>50,38%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>54,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>

--- a/data/trans_orig/CoTrAQ-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33291</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>37504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>29788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33058</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>60094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>244954</t>
+          <t>243323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269328</t>
+          <t>268693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144951</t>
+          <t>144586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168236</t>
+          <t>167393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>398619</t>
+          <t>399551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>430218</t>
+          <t>430428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65934</t>
+          <t>61708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53401</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>38284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>52205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84045</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175200</t>
+          <t>174978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204507</t>
+          <t>203984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110962</t>
+          <t>110544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>265728</t>
+          <t>267522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306908</t>
+          <t>306179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47536</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59255</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199999</t>
+          <t>199024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227342</t>
+          <t>226817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95595</t>
+          <t>96293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287420</t>
+          <t>286427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317899</t>
+          <t>319751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61393</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94884</t>
+          <t>95461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44050</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>71948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114790</t>
+          <t>115872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159649</t>
+          <t>160285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>72839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109403</t>
+          <t>109334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78425</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133022</t>
+          <t>134572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178271</t>
+          <t>180066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222294</t>
+          <t>222669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263544</t>
+          <t>263266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148486</t>
+          <t>146025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180694</t>
+          <t>180075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381762</t>
+          <t>379233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>434523</t>
+          <t>433311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>35602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41708</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>85142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118415</t>
+          <t>118903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46006</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75546</t>
+          <t>72677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59275</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84670</t>
+          <t>86215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69738</t>
+          <t>68010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>95083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136053</t>
+          <t>135888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175280</t>
+          <t>173487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159502</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214712</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>132265</t>
+          <t>131060</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>305181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375033</t>
+          <t>373668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190051</t>
+          <t>189788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>247193</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134966</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>184050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>333165</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>411728</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>944768</t>
+          <t>945134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1016177</t>
+          <t>1012419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>563741</t>
+          <t>562357</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>621024</t>
+          <t>620636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1521554</t>
+          <t>1526867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1616962</t>
+          <t>1620120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39854</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67385</t>
+          <t>68496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>58106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>56213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68139</t>
+          <t>67705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103645</t>
+          <t>103379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190438</t>
+          <t>189922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221409</t>
+          <t>222740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131058</t>
+          <t>131048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158443</t>
+          <t>159252</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>333105</t>
+          <t>332083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373096</t>
+          <t>373327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63642</t>
+          <t>63292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>77239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93823</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130130</t>
+          <t>132093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>39411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63476</t>
+          <t>65664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75466</t>
+          <t>73227</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108875</t>
+          <t>108724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128453</t>
+          <t>127930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159932</t>
+          <t>159792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73376</t>
+          <t>72871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>99625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210267</t>
+          <t>210288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253297</t>
+          <t>254039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27618</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>51110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>53847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54970</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130451</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158535</t>
+          <t>158432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>50821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62432</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186172</t>
+          <t>186019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217551</t>
+          <t>217451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122429</t>
+          <t>121127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163023</t>
+          <t>161577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98657</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>135756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230886</t>
+          <t>228848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282588</t>
+          <t>283812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113760</t>
+          <t>115267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154442</t>
+          <t>154702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69656</t>
+          <t>68863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101563</t>
+          <t>100083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193275</t>
+          <t>194962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244303</t>
+          <t>245463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191548</t>
+          <t>188694</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235631</t>
+          <t>236002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150120</t>
+          <t>149385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186458</t>
+          <t>187094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356214</t>
+          <t>352678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>412713</t>
+          <t>407979</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>74787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102766</t>
+          <t>103218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75980</t>
+          <t>76899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105236</t>
+          <t>104104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159626</t>
+          <t>158872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199387</t>
+          <t>198936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52278</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61987</t>
+          <t>62464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73991</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>106797</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52442</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78823</t>
+          <t>79764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47353</t>
+          <t>46120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73127</t>
+          <t>71349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104706</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>142961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>377903</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266129</t>
+          <t>267707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>328721</t>
+          <t>326543</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>594896</t>
+          <t>599801</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>685604</t>
+          <t>687326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>273677</t>
+          <t>275003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>335916</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>195677</t>
+          <t>196058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>253125</t>
+          <t>248706</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>485297</t>
+          <t>485342</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>575416</t>
+          <t>568989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6206,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>737475</t>
+          <t>736907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>811516</t>
+          <t>811385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>481385</t>
+          <t>484256</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>547675</t>
+          <t>551246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1239293</t>
+          <t>1239560</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1338224</t>
+          <t>1340007</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
